--- a/20-21_KBL_stats.xlsx
+++ b/20-21_KBL_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB8AA9B-B264-42DD-B8CC-D57F65D3DC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21C3A4E-A272-465A-9C7F-7679B7F92094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1785" windowWidth="29040" windowHeight="15720" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="299">
   <si>
     <t>Season</t>
   </si>
@@ -5212,7 +5212,7 @@
         <v>881</v>
       </c>
       <c r="I14" s="23">
-        <f t="shared" ref="I10:I23" si="29">H14/$D14</f>
+        <f t="shared" ref="I14:I23" si="29">H14/$D14</f>
         <v>16.314814814814813</v>
       </c>
       <c r="J14" s="21">
@@ -5493,11 +5493,11 @@
         <v>0.61904761904761907</v>
       </c>
       <c r="M15" s="23">
-        <f t="shared" ref="M10:M23" si="30">K15/$D15</f>
+        <f t="shared" ref="M15:M23" si="30">K15/$D15</f>
         <v>1.7142857142857142</v>
       </c>
       <c r="N15" s="24">
-        <f t="shared" ref="N10:N41" si="31">J15/K15</f>
+        <f t="shared" ref="N15:N41" si="31">J15/K15</f>
         <v>0.3611111111111111</v>
       </c>
       <c r="O15" s="22">
@@ -5756,7 +5756,7 @@
         <v>13</v>
       </c>
       <c r="L16" s="23">
-        <f t="shared" ref="L10:L23" si="32">J16/$D16</f>
+        <f t="shared" ref="L16:L23" si="32">J16/$D16</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="M16" s="23">
@@ -22070,6 +22070,9 @@
       </c>
       <c r="BO77" s="26" t="s">
         <v>150</v>
+      </c>
+      <c r="BQ77" s="36" t="s">
+        <v>258</v>
       </c>
       <c r="BU77" s="60"/>
       <c r="BV77" s="60"/>
